--- a/sso-schema/resources.xlsx
+++ b/sso-schema/resources.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ใบสมัครและไฟล์เรซูเม่ (ข้อมูลส่วนบุคคล) — view = ดูผู้สมัคร ไฟล์ และภาพรวม · edit = เปลี่ยนสถานะ เขียน/ลบโน้ต · manage = ลบใบสมัคร และส่งออก CSV</t>
+          <t>ผู้สมัคร แบบฟอร์มใบสมัคร และผลประเมินสัมภาษณ์ (ข้อมูลส่วนบุคคล) — view = ดูผู้สมัคร ไฟล์ ภาพรวม แบบฟอร์มใบสมัคร ผลประเมินและลิงก์เชิญ พิมพ์ PDF · edit = เปลี่ยนสถานะ เขียน/ลบโน้ต ประเมินสัมภาษณ์ เชิญผู้ประเมิน สร้างลิงก์แก้ไขผลประเมิน · manage = ลบใบสมัคร แบบฟอร์ม และผลประเมิน ส่งออก CSV เห็นข้อมูลอ่อนไหว (PDPA) ในใบสมัคร PDF</t>
         </is>
       </c>
     </row>
